--- a/tame_output/ON/bt/strategyON_20231222.xlsx
+++ b/tame_output/ON/bt/strategyON_20231222.xlsx
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728035</v>
+        <v>3.146730118728034</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -43353,16 +43353,16 @@
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>0.289246809126646</v>
+        <v>0.2890424746503837</v>
       </c>
       <c r="E1819" t="n">
-        <v>3.240715950553319</v>
+        <v>3.240634216762814</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.87139902414949</v>
+        <v>1.871194689673228</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.248213065706103</v>
+        <v>4.248090465020345</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231222.xlsx
+++ b/tame_output/ON/bt/strategyON_20231222.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -628,7 +628,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.4%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -954,11 +954,11 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2023-11-10</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>466.9%</t>
+          <t>452.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-160.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-113.5%</t>
+          <t>-113.9%</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.4%</t>
+          <t>-18.5%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-22.1%</t>
+          <t>-16.3%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>116.2%</t>
+          <t>117.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>111.4%</t>
+          <t>113.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>17.3%</t>
         </is>
       </c>
     </row>
@@ -42433,10 +42433,10 @@
         <v>3.067033934702486</v>
       </c>
       <c r="D1779" t="n">
-        <v>-3.263449867562399</v>
+        <v>-3.325978752447532</v>
       </c>
       <c r="E1779" t="n">
-        <v>1.76129756336378</v>
+        <v>1.736286009409727</v>
       </c>
       <c r="F1779" t="n">
         <v>0.29515364325381</v>
@@ -42456,10 +42456,10 @@
         <v>3.065147691018159</v>
       </c>
       <c r="D1780" t="n">
-        <v>-3.262461185818232</v>
+        <v>-3.324990070703365</v>
       </c>
       <c r="E1780" t="n">
-        <v>1.759806792377119</v>
+        <v>1.734795238423066</v>
       </c>
       <c r="F1780" t="n">
         <v>0.29515364325381</v>
@@ -42473,16 +42473,16 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.12044332578087</v>
+        <v>3.120443325780871</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
       </c>
       <c r="D1781" t="n">
-        <v>-3.254464831296693</v>
+        <v>-3.316993716181826</v>
       </c>
       <c r="E1781" t="n">
-        <v>1.764978960641575</v>
+        <v>1.739967406687522</v>
       </c>
       <c r="F1781" t="n">
         <v>0.3031499977753486</v>
@@ -42502,10 +42502,10 @@
         <v>3.078959898064911</v>
       </c>
       <c r="D1782" t="n">
-        <v>-3.249481080624784</v>
+        <v>-3.312009965509917</v>
       </c>
       <c r="E1782" t="n">
-        <v>1.77881104150125</v>
+        <v>1.753799487547197</v>
       </c>
       <c r="F1782" t="n">
         <v>0.3081337484472573</v>
@@ -42525,10 +42525,10 @@
         <v>3.0856881010767</v>
       </c>
       <c r="D1783" t="n">
-        <v>-3.243094941675229</v>
+        <v>-3.305623826560362</v>
       </c>
       <c r="E1783" t="n">
-        <v>1.788093700092861</v>
+        <v>1.763082146138808</v>
       </c>
       <c r="F1783" t="n">
         <v>0.3081337484472573</v>
@@ -42548,10 +42548,10 @@
         <v>3.089704189836242</v>
       </c>
       <c r="D1784" t="n">
-        <v>-3.254900291993861</v>
+        <v>-3.317429176878994</v>
       </c>
       <c r="E1784" t="n">
-        <v>1.787387648724951</v>
+        <v>1.762376094770898</v>
       </c>
       <c r="F1784" t="n">
         <v>0.2963283981286247</v>
@@ -42571,10 +42571,10 @@
         <v>3.095651647446132</v>
       </c>
       <c r="D1785" t="n">
-        <v>-3.246168481215195</v>
+        <v>-3.308697366100328</v>
       </c>
       <c r="E1785" t="n">
-        <v>1.796827830646307</v>
+        <v>1.771816276692253</v>
       </c>
       <c r="F1785" t="n">
         <v>0.3050602089072909</v>
@@ -42594,10 +42594,10 @@
         <v>3.090962466394117</v>
       </c>
       <c r="D1786" t="n">
-        <v>-3.239831594570743</v>
+        <v>-3.302360479455876</v>
       </c>
       <c r="E1786" t="n">
-        <v>1.794673404252073</v>
+        <v>1.76966185029802</v>
       </c>
       <c r="F1786" t="n">
         <v>0.3050602089072909</v>
@@ -42617,10 +42617,10 @@
         <v>3.100925124196311</v>
       </c>
       <c r="D1787" t="n">
-        <v>-3.237297146843374</v>
+        <v>-3.299826031728508</v>
       </c>
       <c r="E1787" t="n">
-        <v>1.805649841145214</v>
+        <v>1.780638287191161</v>
       </c>
       <c r="F1787" t="n">
         <v>0.3050602089072909</v>
@@ -42640,10 +42640,10 @@
         <v>3.09333980438922</v>
       </c>
       <c r="D1788" t="n">
-        <v>-3.237373045823979</v>
+        <v>-3.299901930709112</v>
       </c>
       <c r="E1788" t="n">
-        <v>1.798034161745882</v>
+        <v>1.773022607791829</v>
       </c>
       <c r="F1788" t="n">
         <v>0.3058234695966178</v>
@@ -42663,10 +42663,10 @@
         <v>3.071104380179594</v>
       </c>
       <c r="D1789" t="n">
-        <v>-3.247875235383325</v>
+        <v>-3.310404120268459</v>
       </c>
       <c r="E1789" t="n">
-        <v>1.771597861712517</v>
+        <v>1.746586307758463</v>
       </c>
       <c r="F1789" t="n">
         <v>0.2953212800372711</v>
@@ -42686,10 +42686,10 @@
         <v>3.071805220025715</v>
       </c>
       <c r="D1790" t="n">
-        <v>-3.249708498062442</v>
+        <v>-3.312237382947575</v>
       </c>
       <c r="E1790" t="n">
-        <v>1.771565396486992</v>
+        <v>1.746553842532939</v>
       </c>
       <c r="F1790" t="n">
         <v>0.2953212800372711</v>
@@ -42709,10 +42709,10 @@
         <v>3.072322299854575</v>
       </c>
       <c r="D1791" t="n">
-        <v>-3.254717613124026</v>
+        <v>-3.317246498009159</v>
       </c>
       <c r="E1791" t="n">
-        <v>1.770078830291218</v>
+        <v>1.745067276337164</v>
       </c>
       <c r="F1791" t="n">
         <v>0.2943267024787364</v>
@@ -42732,10 +42732,10 @@
         <v>3.07155002509494</v>
       </c>
       <c r="D1792" t="n">
-        <v>-3.25842316976084</v>
+        <v>-3.320952054645974</v>
       </c>
       <c r="E1792" t="n">
-        <v>1.767824332876857</v>
+        <v>1.742812778922804</v>
       </c>
       <c r="F1792" t="n">
         <v>0.2924570272211015</v>
@@ -42755,10 +42755,10 @@
         <v>3.071969877157259</v>
       </c>
       <c r="D1793" t="n">
-        <v>-3.257190844403475</v>
+        <v>-3.319719729288608</v>
       </c>
       <c r="E1793" t="n">
-        <v>1.768737115082123</v>
+        <v>1.743725561128069</v>
       </c>
       <c r="F1793" t="n">
         <v>0.2930874035931391</v>
@@ -42778,10 +42778,10 @@
         <v>3.076099785321473</v>
       </c>
       <c r="D1794" t="n">
-        <v>-3.246862847387622</v>
+        <v>-3.309391732272756</v>
       </c>
       <c r="E1794" t="n">
-        <v>1.776998222052677</v>
+        <v>1.751986668098624</v>
       </c>
       <c r="F1794" t="n">
         <v>0.3034154006089912</v>
@@ -42801,10 +42801,10 @@
         <v>3.082620445523309</v>
       </c>
       <c r="D1795" t="n">
-        <v>-3.246746512240067</v>
+        <v>-3.3092753971252</v>
       </c>
       <c r="E1795" t="n">
-        <v>1.783565416313536</v>
+        <v>1.758553862359482</v>
       </c>
       <c r="F1795" t="n">
         <v>0.303531735756547</v>
@@ -42824,10 +42824,10 @@
         <v>3.079594415968698</v>
       </c>
       <c r="D1796" t="n">
-        <v>-3.248591921816934</v>
+        <v>-3.311120806702068</v>
       </c>
       <c r="E1796" t="n">
-        <v>1.779801222928177</v>
+        <v>1.754789668974124</v>
       </c>
       <c r="F1796" t="n">
         <v>0.303531735756547</v>
@@ -42847,10 +42847,10 @@
         <v>3.079532703829831</v>
       </c>
       <c r="D1797" t="n">
-        <v>-3.247093489291835</v>
+        <v>-3.309622374176969</v>
       </c>
       <c r="E1797" t="n">
-        <v>1.78033888379935</v>
+        <v>1.755327329845297</v>
       </c>
       <c r="F1797" t="n">
         <v>0.3050301682816459</v>
@@ -42870,10 +42870,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1798" t="n">
-        <v>-3.255157741484569</v>
+        <v>-3.317686626369702</v>
       </c>
       <c r="E1798" t="n">
-        <v>1.778391160865568</v>
+        <v>1.753379606911515</v>
       </c>
       <c r="F1798" t="n">
         <v>0.296965916088912</v>
@@ -42893,10 +42893,10 @@
         <v>3.080810681773143</v>
       </c>
       <c r="D1799" t="n">
-        <v>-3.256487708945781</v>
+        <v>-3.319016593830915</v>
       </c>
       <c r="E1799" t="n">
-        <v>1.777859173881084</v>
+        <v>1.75284761992703</v>
       </c>
       <c r="F1799" t="n">
         <v>0.296965916088912</v>
@@ -42916,10 +42916,10 @@
         <v>3.083027154880305</v>
       </c>
       <c r="D1800" t="n">
-        <v>-3.02862302621227</v>
+        <v>-3.091151911097404</v>
       </c>
       <c r="E1800" t="n">
-        <v>1.87122152008165</v>
+        <v>1.846209966127597</v>
       </c>
       <c r="F1800" t="n">
         <v>0.296965916088912</v>
@@ -42939,10 +42939,10 @@
         <v>3.090561751225397</v>
       </c>
       <c r="D1801" t="n">
-        <v>-2.780521462345053</v>
+        <v>-2.843050347230187</v>
       </c>
       <c r="E1801" t="n">
-        <v>1.977996741973629</v>
+        <v>1.952985188019575</v>
       </c>
       <c r="F1801" t="n">
         <v>0.296965916088912</v>
@@ -42962,10 +42962,10 @@
         <v>3.091984762198855</v>
       </c>
       <c r="D1802" t="n">
-        <v>-2.483683062951723</v>
+        <v>-2.546211947836857</v>
       </c>
       <c r="E1802" t="n">
-        <v>2.098155112704419</v>
+        <v>2.073143558750365</v>
       </c>
       <c r="F1802" t="n">
         <v>0.4118204045700397</v>
@@ -42985,10 +42985,10 @@
         <v>3.093661836664541</v>
       </c>
       <c r="D1803" t="n">
-        <v>-2.180043506126287</v>
+        <v>-2.24257239101142</v>
       </c>
       <c r="E1803" t="n">
-        <v>2.22128800990028</v>
+        <v>2.196276455946226</v>
       </c>
       <c r="F1803" t="n">
         <v>0.4118204045700397</v>
@@ -43008,10 +43008,10 @@
         <v>3.089601258113999</v>
       </c>
       <c r="D1804" t="n">
-        <v>-1.891022899685578</v>
+        <v>-1.953551784570712</v>
       </c>
       <c r="E1804" t="n">
-        <v>2.332835673926021</v>
+        <v>2.307824119971967</v>
       </c>
       <c r="F1804" t="n">
         <v>0.4118204045700397</v>
@@ -43031,10 +43031,10 @@
         <v>3.094821397458016</v>
       </c>
       <c r="D1805" t="n">
-        <v>-1.606302972421681</v>
+        <v>-1.668831857306814</v>
       </c>
       <c r="E1805" t="n">
-        <v>2.451943784175597</v>
+        <v>2.426932230221544</v>
       </c>
       <c r="F1805" t="n">
         <v>0.6965403318339369</v>
@@ -43054,10 +43054,10 @@
         <v>3.100133560631823</v>
       </c>
       <c r="D1806" t="n">
-        <v>-1.32254130293014</v>
+        <v>-1.385070187815274</v>
       </c>
       <c r="E1806" t="n">
-        <v>2.57076061514602</v>
+        <v>2.545749061191967</v>
       </c>
       <c r="F1806" t="n">
         <v>0.6965403318339369</v>
@@ -43077,10 +43077,10 @@
         <v>3.093376148078457</v>
       </c>
       <c r="D1807" t="n">
-        <v>-1.0608929085375</v>
+        <v>-1.123421793422633</v>
       </c>
       <c r="E1807" t="n">
-        <v>2.66866256034971</v>
+        <v>2.643651006395657</v>
       </c>
       <c r="F1807" t="n">
         <v>0.9581887262265776</v>
@@ -43100,10 +43100,10 @@
         <v>3.090839823094569</v>
       </c>
       <c r="D1808" t="n">
-        <v>-0.7467264703981674</v>
+        <v>-0.8092553552833009</v>
       </c>
       <c r="E1808" t="n">
-        <v>2.791792810621556</v>
+        <v>2.766781256667502</v>
       </c>
       <c r="F1808" t="n">
         <v>1.27235516436591</v>
@@ -43123,10 +43123,10 @@
         <v>3.109254206721308</v>
       </c>
       <c r="D1809" t="n">
-        <v>-0.624214766292395</v>
+        <v>-0.6867436511775286</v>
       </c>
       <c r="E1809" t="n">
-        <v>2.859211875890604</v>
+        <v>2.83420032193655</v>
       </c>
       <c r="F1809" t="n">
         <v>1.394866868471682</v>
@@ -43146,10 +43146,10 @@
         <v>3.119070330776787</v>
       </c>
       <c r="D1810" t="n">
-        <v>-0.4628262323656667</v>
+        <v>-0.5253551172508002</v>
       </c>
       <c r="E1810" t="n">
-        <v>2.933583413516774</v>
+        <v>2.90857185956272</v>
       </c>
       <c r="F1810" t="n">
         <v>1.556255402398411</v>
@@ -43169,10 +43169,10 @@
         <v>3.132597942828719</v>
       </c>
       <c r="D1811" t="n">
-        <v>-0.2830800412171605</v>
+        <v>-0.345608926102294</v>
       </c>
       <c r="E1811" t="n">
-        <v>3.019009502028108</v>
+        <v>2.993997948074055</v>
       </c>
       <c r="F1811" t="n">
         <v>1.556255402398411</v>
@@ -43192,10 +43192,10 @@
         <v>3.139185323079984</v>
       </c>
       <c r="D1812" t="n">
-        <v>-0.1242791147459376</v>
+        <v>-0.1868079996310711</v>
       </c>
       <c r="E1812" t="n">
-        <v>3.089117252867863</v>
+        <v>3.064105698913809</v>
       </c>
       <c r="F1812" t="n">
         <v>1.556255402398411</v>
@@ -43215,10 +43215,10 @@
         <v>3.128096071514691</v>
       </c>
       <c r="D1813" t="n">
-        <v>-0.0314906564405607</v>
+        <v>-0.09401954132569423</v>
       </c>
       <c r="E1813" t="n">
-        <v>3.11514338462472</v>
+        <v>3.090131830670666</v>
       </c>
       <c r="F1813" t="n">
         <v>1.649043860703788</v>
@@ -43238,10 +43238,10 @@
         <v>3.123696569025415</v>
       </c>
       <c r="D1814" t="n">
-        <v>0.06252983893028119</v>
+        <v>9.540451476608425e-07</v>
       </c>
       <c r="E1814" t="n">
-        <v>3.148352080283781</v>
+        <v>3.123340526329728</v>
       </c>
       <c r="F1814" t="n">
         <v>1.658886301196771</v>
@@ -43261,10 +43261,10 @@
         <v>3.109676345532145</v>
       </c>
       <c r="D1815" t="n">
-        <v>0.1526328068368042</v>
+        <v>0.09010392195167072</v>
       </c>
       <c r="E1815" t="n">
-        <v>3.17037304395312</v>
+        <v>3.145361489999067</v>
       </c>
       <c r="F1815" t="n">
         <v>1.661944495484557</v>
@@ -43284,10 +43284,10 @@
         <v>3.127125924287274</v>
       </c>
       <c r="D1816" t="n">
-        <v>0.1967619775583794</v>
+        <v>0.1342330926732459</v>
       </c>
       <c r="E1816" t="n">
-        <v>3.205474290996879</v>
+        <v>3.180462737042825</v>
       </c>
       <c r="F1816" t="n">
         <v>1.745963668471827</v>
@@ -43307,10 +43307,10 @@
         <v>3.126153974671351</v>
       </c>
       <c r="D1817" t="n">
-        <v>0.2065320217360742</v>
+        <v>0.1440031368509407</v>
       </c>
       <c r="E1817" t="n">
-        <v>3.208410359052034</v>
+        <v>3.18339880509798</v>
       </c>
       <c r="F1817" t="n">
         <v>1.825322559526893</v>
@@ -43330,10 +43330,10 @@
         <v>3.115456695754193</v>
       </c>
       <c r="D1818" t="n">
-        <v>0.2431703445040489</v>
+        <v>0.1806414596189154</v>
       </c>
       <c r="E1818" t="n">
-        <v>3.212368409242066</v>
+        <v>3.187356855288013</v>
       </c>
       <c r="F1818" t="n">
         <v>1.825322559526893</v>
@@ -43347,22 +43347,22 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.163076652221068</v>
+        <v>3.159142428300831</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>0.2890424746503837</v>
+        <v>0.2852520862059512</v>
       </c>
       <c r="E1819" t="n">
-        <v>3.240634216762814</v>
+        <v>3.239118061385041</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.871194689673228</v>
+        <v>1.929933186113929</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.248090465020345</v>
+        <v>4.283333562884766</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20231222.xlsx
+++ b/tame_output/ON/bt/strategyON_20231222.xlsx
@@ -901,17 +901,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.0%</t>
+          <t>458.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>-113.9%</t>
+          <t>-119.5%</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.6%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-21.9%</t>
         </is>
       </c>
     </row>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>117.7%</t>
+          <t>116.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>113.2%</t>
+          <t>111.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -42473,7 +42473,7 @@
         <v>45243</v>
       </c>
       <c r="B1781" t="n">
-        <v>3.120443325780871</v>
+        <v>3.12044332578087</v>
       </c>
       <c r="C1781" t="n">
         <v>3.067121317473999</v>
@@ -42634,7 +42634,7 @@
         <v>45250</v>
       </c>
       <c r="B1788" t="n">
-        <v>3.146730118728034</v>
+        <v>3.146730118728035</v>
       </c>
       <c r="C1788" t="n">
         <v>3.09333980438922</v>
@@ -43347,22 +43347,22 @@
         <v>45281</v>
       </c>
       <c r="B1819" t="n">
-        <v>3.159142428300831</v>
+        <v>3.15914242830083</v>
       </c>
       <c r="C1819" t="n">
         <v>3.125373651216407</v>
       </c>
       <c r="D1819" t="n">
-        <v>0.2852520862059512</v>
+        <v>0.2292871380886486</v>
       </c>
       <c r="E1819" t="n">
-        <v>3.239118061385041</v>
+        <v>3.21673208213812</v>
       </c>
       <c r="F1819" t="n">
-        <v>1.929933186113929</v>
+        <v>1.873968237996626</v>
       </c>
       <c r="G1819" t="n">
-        <v>4.283333562884766</v>
+        <v>4.249754594014385</v>
       </c>
     </row>
   </sheetData>
